--- a/ConfigExporter/xlsx/duel_hold_time.xlsx
+++ b/ConfigExporter/xlsx/duel_hold_time.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -443,6 +443,11 @@
           <t>是否无限时间</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>OGS启用</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -465,6 +470,11 @@
           <t>isInfinite</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ogsEnabled</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -487,6 +497,11 @@
           <t>boolean</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -509,6 +524,11 @@
           <t>#require</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -529,6 +549,11 @@
           <t>False</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -549,6 +574,11 @@
           <t>False</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -569,6 +599,11 @@
           <t>False</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -589,6 +624,11 @@
           <t>False</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -607,6 +647,11 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>True</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/ConfigExporter/xlsx/duel_hold_time.xlsx
+++ b/ConfigExporter/xlsx/duel_hold_time.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -533,16 +533,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2m</t>
+          <t>30s</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2分钟</t>
+          <t>30秒</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -558,16 +558,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5m</t>
+          <t>2m</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5分钟</t>
+          <t>2分钟</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -583,16 +583,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10m</t>
+          <t>3m</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10分钟</t>
+          <t>3分钟</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>600</v>
+        <v>180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20m</t>
+          <t>5m</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20分钟</t>
+          <t>5分钟</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -633,23 +633,73 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>10m</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>10分钟</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>600</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20m</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20分钟</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>infinite</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>无限时间</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C11" t="n">
         <v>-1</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/ConfigExporter/xlsx/duel_hold_time.xlsx
+++ b/ConfigExporter/xlsx/duel_hold_time.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -683,23 +683,573 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>30m</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>30分钟</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>40m</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>40分钟</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>50分钟</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>60m</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1小时</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3600</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>70m</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1小时10分</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4200</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>80m</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1小时20分</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4800</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>90m</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1小时30分</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5400</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>100m</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1小时40分</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>110m</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1小时50分</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>6600</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>120m</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2小时</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>7200</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>130m</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2小时10分</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>7800</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>140m</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2小时20分</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>8400</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>150m</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2小时30分</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>160m</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2小时40分</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>9600</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>170m</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2小时50分</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>10200</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>180m</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>3小时</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>190m</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>3小时10分</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>11400</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>200m</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>3小时20分</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>210m</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>3小时30分</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>12600</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>220m</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3小时40分</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>13200</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>230m</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3小时50分</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>13800</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>240m</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>4小时</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>14400</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>infinite</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>无限时间</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C33" t="n">
         <v>-1</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>False</t>
         </is>
